--- a/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-10_Sanction_Screening_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-10_Sanction_Screening_v1.0.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -27936,7 +27936,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1950 (compoff, compchk, ucc, investigator, scrapprover, amlcom1, amlcom2); the others created by the test lead through User Access requests</t>
+          <t>Planned seed V1950 (compoff, compchk, ucc, investigator, scrapprover, amlcom1, amlcom2); the others created by the test lead through User Access requests</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -27961,7 +27961,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1950 of the build design</t>
+          <t>Planned seed V1950 of the build design</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -27986,7 +27986,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1951; invented names only</t>
+          <t>Planned seed V1951; invented names only</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
@@ -28036,7 +28036,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Masked demo clients (V981) plus clients keyed in by the test lead on SIT</t>
+          <t>Masked seed clients (V981) plus clients keyed in by the test lead on SIT</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
@@ -28061,7 +28061,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1952 of the build design</t>
+          <t>Planned seed V1952 of the build design</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
